--- a/data/trans_camb/P1001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,31</t>
+          <t>-2,81; 1,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,99</t>
+          <t>-2,54; 1,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 5,17</t>
+          <t>-2,31; 5,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,32</t>
+          <t>-0,66; 4,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,96</t>
+          <t>-1,76; 2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,03</t>
+          <t>1,46; 11,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,3</t>
+          <t>-1,02; 2,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,66</t>
+          <t>-1,58; 1,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,77</t>
+          <t>0,06; 5,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,4; 101,16</t>
+          <t>-71,57; 105,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,36; 139,53</t>
+          <t>-68,78; 134,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-96,93; 295,82</t>
+          <t>-76,03; 368,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 258,04</t>
+          <t>-26,93; 248,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 187,27</t>
+          <t>-52,15; 178,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,67; 644,51</t>
+          <t>34,6; 571,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 131,46</t>
+          <t>-29,68; 124,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,31; 83,93</t>
+          <t>-45,11; 80,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 285,18</t>
+          <t>-2,38; 289,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,72</t>
+          <t>-2,09; 1,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,41</t>
+          <t>-0,89; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,15</t>
+          <t>-2,89; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 0,99</t>
+          <t>-4,79; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,14</t>
+          <t>-5,31; -0,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 1,81</t>
+          <t>-5,64; 1,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,73</t>
+          <t>-2,62; 0,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,18</t>
+          <t>-2,23; 1,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,64</t>
+          <t>-2,79; 1,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 79,46</t>
+          <t>-51,93; 74,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 143,44</t>
+          <t>-23,54; 139,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,72; 98,79</t>
+          <t>-73,48; 121,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 17,89</t>
+          <t>-53,89; 17,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,61; 5,22</t>
+          <t>-59,86; 0,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 29,22</t>
+          <t>-64,37; 21,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 18,95</t>
+          <t>-44,27; 16,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,76; 27,52</t>
+          <t>-37,06; 25,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 41,07</t>
+          <t>-49,72; 26,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,98</t>
+          <t>-1,33; 3,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,99</t>
+          <t>-1,84; 2,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,31</t>
+          <t>-0,98; 4,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,26</t>
+          <t>1,63; 8,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,74</t>
+          <t>-2,6; 2,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,74</t>
+          <t>-3,56; 1,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,01</t>
+          <t>1,19; 5,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,05</t>
+          <t>-1,6; 2,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,21</t>
+          <t>-1,46; 2,4</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 136,81</t>
+          <t>-27,68; 120,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 105,09</t>
+          <t>-37,4; 110,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 142,89</t>
+          <t>-19,22; 146,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,11; 145,98</t>
+          <t>19,47; 147,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 50,71</t>
+          <t>-32,55; 49,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 34,5</t>
+          <t>-44,64; 25,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,13; 108,16</t>
+          <t>17,2; 111,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 43,7</t>
+          <t>-25,06; 44,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 49,66</t>
+          <t>-22,82; 53,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,02</t>
+          <t>-2,58; 3,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,53</t>
+          <t>-2,42; 3,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,61</t>
+          <t>-5,43; 1,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,25</t>
+          <t>-1,83; 6,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,46</t>
+          <t>-4,52; 3,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,37</t>
+          <t>-5,89; 1,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,88</t>
+          <t>-0,99; 4,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,47</t>
+          <t>-2,34; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,38</t>
+          <t>-5,25; 0,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 87,32</t>
+          <t>-32,09; 83,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 77,01</t>
+          <t>-30,69; 80,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 29,89</t>
+          <t>-70,49; 36,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 68,57</t>
+          <t>-14,16; 72,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 26,99</t>
+          <t>-33,08; 35,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 16,13</t>
+          <t>-42,61; 14,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 52,37</t>
+          <t>-9,67; 59,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 33,46</t>
+          <t>-23,62; 32,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 3,69</t>
+          <t>-53,2; 5,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 5,44</t>
+          <t>-2,74; 5,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,86</t>
+          <t>-4,88; 2,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,37</t>
+          <t>-4,62; 2,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 14,54</t>
+          <t>4,45; 14,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 11,43</t>
+          <t>1,94; 11,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,61</t>
+          <t>-1,59; 5,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,76</t>
+          <t>2,17; 8,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,37</t>
+          <t>-0,18; 5,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,9</t>
+          <t>-1,83; 3,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 83,48</t>
+          <t>-29,48; 80,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 29,18</t>
+          <t>-48,25; 32,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 36,72</t>
+          <t>-42,95; 33,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34,63; 159,62</t>
+          <t>32,62; 158,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,06; 126,76</t>
+          <t>13,04; 130,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 64,23</t>
+          <t>-12,59; 66,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,72; 106,6</t>
+          <t>19,68; 110,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 75,42</t>
+          <t>-1,72; 67,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 35,48</t>
+          <t>-16,42; 40,86</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 5,59</t>
+          <t>-4,77; 5,72</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,8</t>
+          <t>-8,11; 1,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -0,02</t>
+          <t>-9,06; -0,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,86; 14,32</t>
+          <t>3,03; 14,29</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,48</t>
+          <t>1,99; 13,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 2,35</t>
+          <t>-11,94; 2,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,62; 8,56</t>
+          <t>0,74; 8,62</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,1</t>
+          <t>-1,7; 6,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,83; -0,24</t>
+          <t>-10,21; -0,35</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 60,05</t>
+          <t>-34,73; 60,48</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 21,36</t>
+          <t>-56,51; 15,99</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 0,89</t>
+          <t>-58,93; -1,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16,27; 120,02</t>
+          <t>16,65; 118,18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,04; 111,59</t>
+          <t>9,56; 109,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 19,7</t>
+          <t>-70,0; 18,99</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,07; 76,06</t>
+          <t>4,51; 72,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 52,34</t>
+          <t>-11,14; 53,68</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,76; -2,42</t>
+          <t>-68,67; -3,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 13,26</t>
+          <t>-2,5; 12,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 2,37</t>
+          <t>-10,07; 2,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 0,28</t>
+          <t>-11,23; -0,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,98; 20,79</t>
+          <t>7,93; 21,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,52; 16,11</t>
+          <t>2,29; 15,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,65; 12,79</t>
+          <t>2,15; 13,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,87; 15,86</t>
+          <t>6,32; 16,48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,45</t>
+          <t>-1,33; 8,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 6,45</t>
+          <t>-1,7; 5,91</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 102,52</t>
+          <t>-12,63; 93,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 19,73</t>
+          <t>-48,83; 19,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 3,97</t>
+          <t>-54,39; 0,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35,32; 136,21</t>
+          <t>37,31; 138,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,47; 107,43</t>
+          <t>9,35; 103,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,7; 87,68</t>
+          <t>9,57; 91,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,86; 101,06</t>
+          <t>30,01; 104,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 53,47</t>
+          <t>-5,98; 54,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 44,5</t>
+          <t>-8,26; 39,21</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,44</t>
+          <t>-0,15; 2,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,14</t>
+          <t>-1,08; 1,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,98</t>
+          <t>-1,89; 0,96</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,87</t>
+          <t>3,75; 6,91</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,28</t>
+          <t>1,32; 4,35</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,87</t>
+          <t>-0,79; 3,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,23</t>
+          <t>2,18; 4,23</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,46</t>
+          <t>0,53; 2,42</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,68</t>
+          <t>-0,68; 1,74</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 44,46</t>
+          <t>-2,56; 41,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 21,42</t>
+          <t>-15,92; 20,12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 17,42</t>
+          <t>-29,18; 17,48</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37,5; 79,08</t>
+          <t>37,03; 80,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,65; 49,13</t>
+          <t>13,1; 51,36</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 32,27</t>
+          <t>-8,1; 33,81</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,84; 57,87</t>
+          <t>26,56; 57,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,11; 33,39</t>
+          <t>6,18; 33,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 22,98</t>
+          <t>-8,36; 23,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,34</t>
+          <t>-2,55; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,98</t>
+          <t>-2,3; 1,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 5,02</t>
+          <t>-2,34; 4,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,59</t>
+          <t>-0,56; 4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,77</t>
+          <t>-1,87; 2,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 11,15</t>
+          <t>1,61; 10,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,3</t>
+          <t>-1,06; 2,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,57</t>
+          <t>-1,61; 1,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,85</t>
+          <t>0,35; 5,65</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>208,71%</t>
+          <t>195,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,57; 105,42</t>
+          <t>-71,21; 102,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 134,1</t>
+          <t>-68,34; 141,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,03; 368,19</t>
+          <t>-75,11; 227,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 248,86</t>
+          <t>-20,03; 263,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,15; 178,04</t>
+          <t>-52,12; 176,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,6; 571,79</t>
+          <t>35,98; 598,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 124,65</t>
+          <t>-34,15; 100,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 80,65</t>
+          <t>-46,79; 88,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 289,24</t>
+          <t>6,61; 290,12</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,93</t>
+          <t>-2,22; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,44</t>
+          <t>-0,88; 3,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,09</t>
+          <t>-2,9; 1,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,98</t>
+          <t>-4,83; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; -0,02</t>
+          <t>-5,43; 0,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 1,46</t>
+          <t>-4,07; 2,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,71</t>
+          <t>-2,63; 0,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,03</t>
+          <t>-2,25; 1,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,35</t>
+          <t>-2,52; 1,5</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-28,55%</t>
+          <t>-25,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,28%</t>
+          <t>-14,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,79%</t>
+          <t>-14,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 74,46</t>
+          <t>-53,29; 68,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 139,85</t>
+          <t>-24,08; 139,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 121,84</t>
+          <t>-74,51; 84,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 17,42</t>
+          <t>-53,67; 20,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,86; 0,47</t>
+          <t>-59,07; 5,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,37; 21,92</t>
+          <t>-47,22; 40,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 16,49</t>
+          <t>-44,69; 17,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 25,77</t>
+          <t>-38,15; 31,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,72; 26,85</t>
+          <t>-43,93; 38,0</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,71</t>
+          <t>-1,04; 3,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,95</t>
+          <t>-1,82; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,51</t>
+          <t>-1,28; 3,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,02</t>
+          <t>1,63; 7,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,65</t>
+          <t>-2,73; 2,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,41</t>
+          <t>-3,4; 1,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,28</t>
+          <t>0,94; 5,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,01</t>
+          <t>-1,59; 2,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,4</t>
+          <t>-1,61; 2,05</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,03%</t>
+          <t>-9,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 120,65</t>
+          <t>-21,53; 128,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 110,91</t>
+          <t>-35,76; 111,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 146,83</t>
+          <t>-25,25; 135,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,47; 147,13</t>
+          <t>19,81; 148,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 49,25</t>
+          <t>-34,43; 50,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 25,67</t>
+          <t>-40,8; 33,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,2; 111,94</t>
+          <t>13,57; 110,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 44,86</t>
+          <t>-25,08; 45,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 53,63</t>
+          <t>-25,48; 44,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-1,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,67</t>
+          <t>-2,51; 3,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,57</t>
+          <t>-2,59; 3,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,87</t>
+          <t>-2,87; 2,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,65</t>
+          <t>-1,98; 6,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 3,18</t>
+          <t>-4,89; 2,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,33</t>
+          <t>-5,49; 0,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,19</t>
+          <t>-1,1; 3,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,42</t>
+          <t>-2,46; 2,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,54</t>
+          <t>-3,21; 1,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-21,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,76%</t>
+          <t>-20,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-22,86%</t>
+          <t>-11,61%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 83,96</t>
+          <t>-34,93; 79,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 80,02</t>
+          <t>-33,81; 81,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 36,91</t>
+          <t>-35,95; 62,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 72,82</t>
+          <t>-14,73; 68,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 35,9</t>
+          <t>-35,09; 31,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 14,21</t>
+          <t>-40,85; 7,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 59,9</t>
+          <t>-11,45; 51,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 32,36</t>
+          <t>-24,78; 33,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 5,65</t>
+          <t>-31,14; 16,91</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,24</t>
+          <t>-2,68; 5,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,07</t>
+          <t>-5,06; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,19</t>
+          <t>-4,87; 1,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,45; 14,17</t>
+          <t>4,47; 15,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,69</t>
+          <t>1,99; 11,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,74</t>
+          <t>-1,14; 6,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,84</t>
+          <t>2,36; 8,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,55</t>
+          <t>-0,51; 5,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,22</t>
+          <t>-1,87; 3,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-9,65%</t>
+          <t>-13,93%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 80,75</t>
+          <t>-25,35; 88,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 32,99</t>
+          <t>-49,26; 27,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 33,67</t>
+          <t>-46,28; 31,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32,62; 158,27</t>
+          <t>32,87; 173,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,04; 130,3</t>
+          <t>13,72; 133,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 66,14</t>
+          <t>-9,12; 73,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,68; 110,18</t>
+          <t>20,57; 107,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 67,45</t>
+          <t>-4,55; 63,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 40,86</t>
+          <t>-16,54; 40,27</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-4,23</t>
+          <t>-4,32</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-1,35</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,72</t>
+          <t>-5,02; 5,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,26</t>
+          <t>-8,08; 1,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -0,34</t>
+          <t>-8,78; -0,41</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,03; 14,29</t>
+          <t>2,87; 14,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,99; 13,22</t>
+          <t>1,83; 13,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 2,36</t>
+          <t>-2,95; 5,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,62</t>
+          <t>0,95; 8,54</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,3</t>
+          <t>-1,24; 5,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -0,35</t>
+          <t>-4,28; 1,76</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-35,31%</t>
+          <t>-36,07%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-29,38%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-30,43%</t>
+          <t>-10,28%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 60,48</t>
+          <t>-35,77; 59,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 15,99</t>
+          <t>-56,44; 12,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,93; -1,72</t>
+          <t>-58,41; -2,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16,65; 118,18</t>
+          <t>16,01; 120,24</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,56; 109,87</t>
+          <t>10,99; 112,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 18,99</t>
+          <t>-17,6; 51,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,51; 72,86</t>
+          <t>5,16; 73,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 53,68</t>
+          <t>-8,62; 51,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,67; -3,93</t>
+          <t>-28,25; 16,96</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-5,23</t>
+          <t>-4,73</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,84</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 12,37</t>
+          <t>-1,41; 13,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 2,53</t>
+          <t>-10,96; 1,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -0,03</t>
+          <t>-11,45; 0,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,93; 21,4</t>
+          <t>7,71; 21,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,29; 15,97</t>
+          <t>1,81; 15,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,15; 13,29</t>
+          <t>2,33; 13,59</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,32; 16,48</t>
+          <t>6,32; 16,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 8,51</t>
+          <t>-0,71; 8,9</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 5,91</t>
+          <t>-1,19; 7,08</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-31,17%</t>
+          <t>-28,23%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 93,46</t>
+          <t>-8,34; 98,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 19,67</t>
+          <t>-52,55; 15,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 0,09</t>
+          <t>-51,91; 3,11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37,31; 138,41</t>
+          <t>35,25; 141,47</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,35; 103,56</t>
+          <t>8,14; 100,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,57; 91,88</t>
+          <t>9,7; 89,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,01; 104,05</t>
+          <t>30,23; 106,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 54,93</t>
+          <t>-3,92; 58,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 39,21</t>
+          <t>-5,61; 47,5</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,3</t>
+          <t>-0,16; 2,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,14</t>
+          <t>-1,19; 1,11</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,96</t>
+          <t>-1,21; 1,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,91</t>
+          <t>3,6; 6,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,35</t>
+          <t>1,19; 4,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,0</t>
+          <t>0,89; 3,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,23</t>
+          <t>2,15; 4,22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,42</t>
+          <t>0,49; 2,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,74</t>
+          <t>0,32; 2,24</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-4,9%</t>
+          <t>-0,26%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 41,44</t>
+          <t>-2,44; 44,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 20,12</t>
+          <t>-18,07; 21,52</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 17,48</t>
+          <t>-18,36; 21,34</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37,03; 80,95</t>
+          <t>35,14; 75,35</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>13,1; 51,36</t>
+          <t>11,89; 51,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 33,81</t>
+          <t>8,65; 41,32</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,56; 57,2</t>
+          <t>25,88; 58,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,18; 33,07</t>
+          <t>6,0; 32,22</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 23,3</t>
+          <t>3,79; 31,43</t>
         </is>
       </c>
     </row>
